--- a/docs/codeability_review.xlsx
+++ b/docs/codeability_review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,7 +513,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -564,7 +563,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -814,7 +813,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -864,7 +863,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -914,7 +913,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -939,7 +938,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -964,7 +963,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -983,7 +982,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Face Sheet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -996,57 +995,57 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A demographic page that fits neither of the above.</t>
+          <t>The printed face sheet or registration page. Note that this overlaps Patient Demographics by design: both were asked for, and a face sheet is in practice the demographics page under another name.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Discharge Summary</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consultation Note</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Discharge</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Inpatient consult. Office consults are Progress Note.</t>
+          <t>A demographic page that fits neither of the above.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Discharge Summary</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Depart/Discharge Note</t>
+          <t>Patient Information</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Discharge</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The discharge summary itself, in any of its names: depart note, depart summary, discharge note, discharge report, final case summary.</t>
+          <t>The patient's identity, contact and coverage details.</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1057,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Discharge Diagnosis</t>
+          <t>Consultation Note</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1071,7 +1070,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Discharge Diagnosis.</t>
+          <t>Inpatient consult. Office consults are Progress Note.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1082,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Discharge Instruction</t>
+          <t>Depart/Discharge Note</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1096,7 +1095,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>What the patient was told to do after discharge, including the Spanish-language versions of the same form.</t>
+          <t>The discharge summary itself, in any of its names: depart note, depart summary, discharge note, discharge report, final case summary.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1107,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Discharge Medication</t>
+          <t>Discharge Diagnosis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1121,7 +1120,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>The medication list as it stands at discharge.</t>
+          <t>Discharge Diagnosis.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1132,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>History and Physical</t>
+          <t>Discharge Instruction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1146,7 +1145,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Admission H&amp;P of an inpatient, observation or short stay. Office H&amp;Ps are Progress Note.</t>
+          <t>What the patient was told to do after discharge, including the Spanish-language versions of the same form.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1157,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Interim Summary</t>
+          <t>Discharge Medication</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1171,7 +1170,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A summary issued mid-stay rather than at discharge.</t>
+          <t>The medication list as it stands at discharge.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1182,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>History and Physical</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1196,7 +1195,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A discharge-packet page that fits none of the above.</t>
+          <t>Admission H&amp;P of an inpatient, observation or short stay. Office H&amp;Ps are Progress Note.</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1207,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Short Stay Summary</t>
+          <t>Interim Summary</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1221,7 +1220,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>The discharge document for a short stay or observation episode. Its own header governs even where it embeds a history and physical.</t>
+          <t>A summary issued mid-stay rather than at discharge.</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1232,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transfer of Care</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1246,57 +1245,57 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Handover to another facility or service, including anaesthesia transfer of care.</t>
+          <t>A discharge-packet page that fits none of the above.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forms and Questionnaires</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Short Stay Summary</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Discharge</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A structured assessment or evaluation: functional status, ADL and IADL, nutrition, occupational health, fitness for duty, annual wellness.</t>
+          <t>The discharge document for a short stay or observation episode. Its own header governs even where it embeds a history and physical.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forms and Questionnaires</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Transfer of Care</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Discharge</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A form that is neither clearly a questionnaire nor clearly an assessment.</t>
+          <t>Handover to another facility or service, including anaesthesia transfer of care.</t>
         </is>
       </c>
     </row>
@@ -1308,32 +1307,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A questionnaire, checklist or screening instrument completed about the patient: screening tests, preventive checklists, health maintenance, Mini-Cog and clock drawing, growth charts.</t>
+          <t>A structured assessment or evaluation: functional status, ADL and IADL, nutrition, occupational health, fitness for duty, annual wellness.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Forms and Questionnaires</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Immunization Record</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1346,19 +1345,19 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vaccines given or due, in any format: immunisation list, vaccination administration record, flu shot record.</t>
+          <t>A form that is neither clearly a questionnaire nor clearly an assessment.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Forms and Questionnaires</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1371,19 +1370,19 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>An immunisation page that fits none of the above.</t>
+          <t>A questionnaire, checklist or screening instrument completed about the patient: screening tests, preventive checklists, health maintenance, Mini-Cog and clock drawing, growth charts.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Immunization Record</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1396,26 +1395,22 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Vaccines given or due, in any format: immunisation list, vaccination administration record, flu shot record.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ankle-Brachial Index Report</t>
-        </is>
-      </c>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -1425,7 +1420,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ankle-Brachial Index Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>An immunisation page that fits none of the above.</t>
         </is>
       </c>
     </row>
@@ -1440,11 +1435,7 @@
           <t>Diagnostic Study</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Audiogram and Hearing Loss Report</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -1454,7 +1445,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Audiogram and Hearing Loss Report.</t>
+          <t>Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1462,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Behavioral Assessment</t>
+          <t>Ankle-Brachial Index Report</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1483,7 +1474,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Behavioral Assessment.</t>
+          <t>Ankle-Brachial Index Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1491,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bronchoscopy Report</t>
+          <t>Audiogram and Hearing Loss Report</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1512,7 +1503,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bronchoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Audiogram and Hearing Loss Report.</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1520,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cardiac Catheterization Report</t>
+          <t>Behavioral Assessment</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1541,7 +1532,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cardiac Catheterization Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Behavioral Assessment.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1549,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Carotid Duplex Report</t>
+          <t>Bronchoscopy Report</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1570,7 +1561,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carotid Duplex Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Bronchoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1578,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Colonoscopy Report</t>
+          <t>Cardiac Catheterization Report</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1599,7 +1590,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Colonoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Cardiac Catheterization Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1607,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Corneal Topography</t>
+          <t>Carotid Duplex Report</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1628,7 +1619,7 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corneal Topography.</t>
+          <t>Carotid Duplex Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1636,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cystoscopy Report</t>
+          <t>Colonoscopy Report</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1657,7 +1648,7 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Colonoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1665,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Doppler Duplex Report</t>
+          <t>Corneal Topography</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1686,7 +1677,7 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Doppler Duplex Report.</t>
+          <t>Corneal Topography.</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1694,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Echocardiogram Report</t>
+          <t>Cystoscopy Report</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1715,7 +1706,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Echocardiogram Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Cystoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1723,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Electrocardiogram (EKG/ECG) Report</t>
+          <t>Doppler Duplex Report</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1744,7 +1735,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Electrocardiogram. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Doppler Duplex Report.</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1752,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Electroencephalogram Report</t>
+          <t>Echocardiogram Report</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1773,7 +1764,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Electroencephalogram Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Echocardiogram Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1781,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Electromyography and Nerve Conduction</t>
+          <t>Electrocardiogram (EKG/ECG) Report</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1802,7 +1793,7 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Electromyography and Nerve Conduction. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Electrocardiogram. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1810,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Endoscopy Report</t>
+          <t>Electroencephalogram Report</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1831,7 +1822,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Endoscopy Report.</t>
+          <t>Electroencephalogram Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1839,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Esophageal Manometry Report</t>
+          <t>Electromyography and Nerve Conduction</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1860,7 +1851,7 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Esophageal Manometry Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Electromyography and Nerve Conduction. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1868,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Esophagogastroduodenoscopy (EGD) Report</t>
+          <t>Endoscopy Report</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1889,7 +1880,7 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Esophagogastroduodenoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Endoscopy Report.</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1897,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Extremity Doppler Report</t>
+          <t>Esophageal Manometry Report</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1918,7 +1909,7 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Extremity Doppler Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Esophageal Manometry Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1926,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Holter Monitor Report</t>
+          <t>Esophagogastroduodenoscopy (EGD) Report</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1947,7 +1938,7 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Holter Monitor Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Esophagogastroduodenoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1955,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Laryngoscopy Procedure Report</t>
+          <t>Extremity Doppler Report</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1976,7 +1967,7 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Laryngoscopy Procedure Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Extremity Doppler Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1984,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Neurocognitive Screening Examination</t>
+          <t>Holter Monitor Report</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,7 +1996,7 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neurocognitive Screening Examination. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Holter Monitor Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2013,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Optical Biometry (IOL Calculation)</t>
+          <t>Laryngoscopy Procedure Report</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2034,7 +2025,7 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Optical Biometry (IOL Calculation).</t>
+          <t>Laryngoscopy Procedure Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2042,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Optical Coherence Tomography Report</t>
+          <t>Neurocognitive Screening Examination</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2063,7 +2054,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Optical Coherence Tomography Report.</t>
+          <t>Neurocognitive Screening Examination. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2071,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Optical Biometry (IOL Calculation)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2092,7 +2083,7 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A diagnostic study with no more specific type identified. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Optical Biometry (IOL Calculation).</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2100,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oximetry Report</t>
+          <t>Optical Coherence Tomography Report</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2121,7 +2112,7 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Oximetry Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Optical Coherence Tomography Report.</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2129,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pacemaker Device Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2150,7 +2141,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pacemaker Device Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>A diagnostic study with no more specific type identified. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2158,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plethysmography Report</t>
+          <t>Oximetry Report</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2179,7 +2170,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Plethysmography Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Oximetry Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2187,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test</t>
+          <t>Pacemaker Device Report</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2208,7 +2199,7 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Pacemaker Device Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2216,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sigmoidoscopy Report</t>
+          <t>Plethysmography Report</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2237,7 +2228,7 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sigmoidoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Plethysmography Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2245,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sleep Study Report</t>
+          <t>Pulmonary Function Test</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2266,7 +2257,7 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sleep Study Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Pulmonary Function Test. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2274,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Split Night Study Report</t>
+          <t>Sigmoidoscopy Report</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2295,7 +2286,7 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Split Night Study Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Sigmoidoscopy Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2303,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Stress Test</t>
+          <t>Sleep Study Report</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2324,7 +2315,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Stress Test Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Sleep Study Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2332,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sudoscan Report</t>
+          <t>Split Night Study Report</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2353,7 +2344,7 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sudoscan Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Split Night Study Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2361,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telemetry Report</t>
+          <t>Stress Test</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2382,7 +2373,7 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Telemetry Report.</t>
+          <t>Stress Test Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2390,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Titration Report</t>
+          <t>Sudoscan Report</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2411,7 +2402,7 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Titration Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Sudoscan Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2419,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Videonystagmography Report</t>
+          <t>Telemetry Report</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2440,7 +2431,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Videonystagmography Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
+          <t>Telemetry Report.</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2448,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Visual Field Report</t>
+          <t>Titration Report</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2469,7 +2460,7 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Visual Field Report.</t>
+          <t>Titration Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2481,10 +2472,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Diagnostic Study</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Videonystagmography Report</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -2494,7 +2489,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Videonystagmography Report. Any other study that produces a report: cardiac, neurological, pulmonary, sleep, vascular, endoscopic and ophthalmic. Deliberately broad. It holds many service lines at once, which is why no single specialty is implied at this level and the specialty is read from the page instead.</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2501,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Allergy Testing Report</t>
+          <t>Visual Field Report</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2523,7 +2518,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Allergy Testing Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Visual Field Report.</t>
         </is>
       </c>
     </row>
@@ -2538,11 +2533,7 @@
           <t>Lab Result</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Chemistry Report</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -2552,7 +2543,7 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chemistry Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2560,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Coagulation Report</t>
+          <t>Allergy Testing Report</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2581,7 +2572,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>INR and Prothrombin Time. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Allergy Testing Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2589,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FISH Report</t>
+          <t>Chemistry Report</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2610,7 +2601,7 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FISH Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Chemistry Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2618,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Genetic Test Report</t>
+          <t>Coagulation Report</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2639,7 +2630,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Genetic Test Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>INR and Prothrombin Time. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2647,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Glucose Report</t>
+          <t>FISH Report</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2668,7 +2659,7 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Glucose Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>FISH Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2676,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hematology Report</t>
+          <t>Genetic Test Report</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2697,7 +2688,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hematology Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Genetic Test Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2705,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Laboratory Flow Sheet</t>
+          <t>Glucose Report</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2726,7 +2717,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Laboratory Flow Sheet. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Glucose Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2734,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Microbiology Report</t>
+          <t>Hematology Report</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2755,7 +2746,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microbiology Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Hematology Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Laboratory Flow Sheet</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2784,7 +2775,7 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>A laboratory with no more specific type identified. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Laboratory Flow Sheet. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2792,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Urinalysis Report</t>
+          <t>Microbiology Report</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2813,7 +2804,7 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Urinalysis Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
+          <t>Microbiology Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2816,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Biopsy Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2842,7 +2833,7 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Biopsy Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
+          <t>A laboratory with no more specific type identified. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2845,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cytology Report</t>
+          <t>Urinalysis Report</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2871,7 +2862,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cytology Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
+          <t>Urinalysis Report. Specimen-based testing: chemistry, haematology, microbiology, urinalysis, genetics, coagulation.</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2879,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cytometry Report</t>
+          <t>Biopsy Report</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2900,7 +2891,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cytometry Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
+          <t>Biopsy Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2908,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Molecular Diagnostics Report</t>
+          <t>Cytology Report</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2929,7 +2920,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Molecular Diagnostics Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
+          <t>Cytology Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2937,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Cytometry Report</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2958,7 +2949,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>A pathology with no more specific type identified. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
+          <t>Cytometry Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2970,10 +2961,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>Pathology Report</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Molecular Diagnostics Report</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -2983,7 +2978,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Molecular Diagnostics Report. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2990,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Pathology Report</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bone Mineral Density Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3012,7 +3007,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bone Mineral Density Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>A pathology with no more specific type identified. Tissue and cell examination: biopsy, cytology, flow cytometry, molecular diagnostics.</t>
         </is>
       </c>
     </row>
@@ -3027,11 +3022,7 @@
           <t>Radiology Report</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Brain MRI Report</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -3041,7 +3032,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Brain MRI Report.</t>
+          <t>Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3049,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CT Angiography Report</t>
+          <t>Bone Mineral Density Report</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3070,7 +3061,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CT Angiography Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Bone Mineral Density Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CT Scan Report</t>
+          <t>Brain MRI Report</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3099,7 +3090,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CT Scan Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Brain MRI Report.</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3107,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MR Angiography Report</t>
+          <t>CT Scan Report</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3128,7 +3119,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MR Angiography Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>CT Scan Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3136,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>MR Angiography Report</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3157,7 +3148,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MRI Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>MR Angiography Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3165,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mammogram Report</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3186,7 +3177,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mammogram Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>MRI Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3194,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Report</t>
+          <t>Mammogram Report</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3215,7 +3206,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Mammogram Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3223,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Nuclear Medicine Report</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3244,7 +3235,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>A radiology with no more specific type identified. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Nuclear Medicine Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3252,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3273,7 +3264,7 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ultrasound Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>A radiology with no more specific type identified. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3281,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>X-Ray Report</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3302,22 +3293,26 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>X-Ray Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Ultrasound Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Medication Record</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Blood Transfusion Record</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>Radiology Report</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>X-Ray Report</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -3327,7 +3322,7 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Administration of blood or blood products, which is a medication administration rather than a procedure.</t>
+          <t>X-Ray Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3334,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Blood Transfusion Record</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -3352,7 +3347,7 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>The current medication list as a standalone page.</t>
+          <t>Administration of blood or blood products, which is a medication administration rather than a procedure.</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3359,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -3377,7 +3372,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>A medication page that fits none of the above.</t>
+          <t>The current medication list as a standalone page.</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3384,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Prescription Page</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -3402,7 +3397,7 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>A prescription or Rx page.</t>
+          <t>A medication page that fits none of the above.</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3409,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Refill Record</t>
+          <t>Prescription Page</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -3427,82 +3422,82 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>A record of refills issued.</t>
+          <t>A prescription or Rx page.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Implant Record</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Implant log or sticker page: devices, lot numbers.</t>
+          <t>A record of refills issued.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Intra-operative Record</t>
+          <t>Laboratory Requisition</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Intra-operative nursing / OR record: times, staff, positioning, counts.</t>
+          <t>A requisition or lab form requesting a test.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Post-operative</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Post-operative.</t>
+          <t>An order or request that fits neither of the above.</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3509,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Laboratory Requisition</t>
+          <t>Physician Order</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -3527,7 +3522,7 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>A requisition or lab form requesting a test.</t>
+          <t>Any order written by a clinician: medication, treatment, service request, post-operative orders.</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3534,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -3552,19 +3547,19 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>An order or request that fits neither of the above.</t>
+          <t>Referral Order.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Order and Requisition</t>
+          <t>Patient Communication</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -3577,32 +3572,32 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Any order written by a clinician: medication, treatment, service request, post-operative orders.</t>
+          <t>A notice or notification sent to the patient, including discharge notices.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Order and Requisition</t>
+          <t>Patient Communication</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Referral Order</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Referral Order.</t>
+          <t>A communication page that fits none of the above.</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3609,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Patient Education Material</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -3627,7 +3622,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>A notice or notification sent to the patient, including discharge notices.</t>
+          <t>Educational material and patient instructions given out as their own document.</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3634,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Patient Message</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3652,7 +3647,7 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>A communication page that fits none of the above.</t>
+          <t>A message exchanged with the patient: telephone message, portal communication, web encounter.</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3659,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Telephone Encounter</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -3677,19 +3672,19 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Educational material and patient instructions given out as their own document.</t>
+          <t>Phone note, refill call, telephone message.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Patient Message</t>
+          <t>Diagnosis List/Index</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -3702,19 +3697,19 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>A message exchanged with the patient: telephone message, portal communication, web encounter.</t>
+          <t>A list or index of diagnoses, often coded, with no assessment.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Telephone Encounter</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -3727,7 +3722,7 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phone note, refill call, telephone message.</t>
+          <t>Others.</t>
         </is>
       </c>
     </row>
@@ -3739,32 +3734,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Diagnosis List/Index</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
+          <t>Non-Codable</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>A list or index of diagnoses, often coded, with no assessment.</t>
+          <t>A standing problem list page.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Provider Letter</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Consultation Letter</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3777,19 +3772,19 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Others.</t>
+          <t>Consultant letter back to the referring provider.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Provider Letter</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3802,7 +3797,7 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>A standing problem list page.</t>
+          <t>Others.</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Consultation Letter</t>
+          <t>Records Request</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3827,7 +3822,7 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Consultant letter back to the referring provider.</t>
+          <t>Any letter, fax or EHR note whose purpose is requesting records.</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3834,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Referral Letter</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3852,64 +3847,14 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Others.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Provider Letter</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Records Request</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Non-Codable</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Any letter, fax or EHR note whose purpose is requesting records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Provider Letter</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Referral Letter</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Non-Codable</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
           <t>Letter referring the patient to another provider.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 E106 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E119 E120 E121 E122 E123 E124 E125 E126 E127 E128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Codable,Non-Codable,Discharge,Needs review"</formula1>
+    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 E106 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E119 E120 E121 E122 E123 E124 E125 E126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Codable,Non-Codable,Discharge"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3922,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3932,7 +3877,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3963,15 +3907,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Your call</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Your call</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -3999,13 +3938,8 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4025,13 +3959,8 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4055,13 +3984,8 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4085,13 +4009,8 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4115,13 +4034,8 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4142,16 +4056,11 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4172,16 +4081,11 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4202,21 +4106,16 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Patient Registration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4226,7 +4125,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Patient Registration</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4235,18 +4134,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Superbill</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4256,7 +4150,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Superbill</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -4265,28 +4159,23 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>After-Visit Summary</t>
+          <t>Superbill</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clinical Summary</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>After-Visit Summary</t>
+          <t>Superbill</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -4295,48 +4184,38 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>After-Visit Summary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Clinical Summary</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Clinical Summary</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>After-Visit Summary</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Clinical Summary (class words)</t>
+          <t>Clinical Summary</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4344,25 +4223,24 @@
           <t>Clinical Summary</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Summary of Care (C-CDA)</t>
+          <t>Clinical Summary (class words)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4370,39 +4248,30 @@
           <t>Clinical Summary</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Summary of Care (C-CDA)</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Assignment of Benefits</t>
+          <t>Summary of Care (C-CDA)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consent and Authorization</t>
+          <t>Clinical Summary</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Assignment of Benefits</t>
+          <t>Summary of Care (C-CDA)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -4411,18 +4280,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Authorization Form</t>
+          <t>Assignment of Benefits</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4432,7 +4296,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>General Authorization</t>
+          <t>Assignment of Benefits</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -4441,18 +4305,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Consent Form</t>
+          <t>Authorization Form</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4462,7 +4321,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>General Consent</t>
+          <t>General Authorization</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -4471,44 +4330,38 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Consent Form</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Consent and Authorization</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Consent and Authorization</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>General Consent</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Consent for Treatment</t>
+          <t>Consent and Authorization</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4516,29 +4369,20 @@
           <t>Consent and Authorization</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Consent for Treatment</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HIPAA Form</t>
+          <t>Consent for Treatment</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4548,7 +4392,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HIPAA and Privacy</t>
+          <t>Consent for Treatment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -4557,18 +4401,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Immunization Consent Form</t>
+          <t>HIPAA Form</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4578,7 +4417,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Immunization Consent</t>
+          <t>HIPAA and Privacy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -4587,18 +4426,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Insurance Authorization Form</t>
+          <t>Immunization Consent Form</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4608,7 +4442,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Referral Authorization</t>
+          <t>Immunization Consent</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -4617,18 +4451,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Patient Agreement Form</t>
+          <t>Insurance Authorization Form</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4638,7 +4467,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>General Consent</t>
+          <t>Referral Authorization</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -4647,18 +4476,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Policy Page</t>
+          <t>Patient Agreement Form</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4677,18 +4501,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Prior Authorization Request</t>
+          <t>Policy Page</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4698,7 +4517,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prior Authorization</t>
+          <t>General Consent</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -4707,18 +4526,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Referral &amp; Authorization</t>
+          <t>Prior Authorization Request</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4728,7 +4542,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Referral Authorization</t>
+          <t>Prior Authorization</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -4737,18 +4551,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Referral Authorization</t>
+          <t>Referral &amp; Authorization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4767,18 +4576,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Referral Authorization Form</t>
+          <t>Referral Authorization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4797,18 +4601,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Referral Request</t>
+          <t>Referral Authorization Form</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4827,18 +4626,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Referral authorization form</t>
+          <t>Referral Request</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4857,18 +4651,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Release of Information Authorization</t>
+          <t>Referral authorization form</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4878,7 +4667,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Release of Information</t>
+          <t>Referral Authorization</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4887,18 +4676,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Surgical Consent Form</t>
+          <t>Release of Information Authorization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4908,7 +4692,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Surgical Consent</t>
+          <t>Release of Information</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -4917,18 +4701,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Transfusion Consent Form</t>
+          <t>Surgical Consent Form</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4938,7 +4717,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Transfusion Consent</t>
+          <t>Surgical Consent</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -4947,174 +4726,144 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Demographics</t>
+          <t>Transfusion Consent Form</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Demographics</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Consent and Authorization</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Transfusion Consent</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Consultation Note</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Discharge Summary</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Consultation Note</t>
-        </is>
-      </c>
+          <t>Demographics</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Discharge</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Depart Note</t>
+          <t>Face Sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Discharge Summary</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Depart/Discharge Note</t>
+          <t>Face Sheet</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Discharge</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Discharge Instructions</t>
+          <t>Patient Demographics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Discharge Summary</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Discharge Instruction</t>
+          <t>Patient Information</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Discharge</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Discharge Medication</t>
+          <t>Patient Information</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Discharge Summary</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Discharge Medication</t>
+          <t>Patient Information</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Discharge</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Consultation Note</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Discharge Summary</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Discharge Summary</t>
-        </is>
-      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Depart/Discharge Note</t>
+          <t>Consultation Note</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -5123,18 +4872,13 @@
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Discharge Summary (class words)</t>
+          <t>Depart Note</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5142,25 +4886,24 @@
           <t>Discharge Summary</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Depart/Discharge Note</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Final Case Summary</t>
+          <t>Discharge Instructions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5170,7 +4913,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Depart/Discharge Note</t>
+          <t>Discharge Instruction</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -5179,18 +4922,13 @@
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>History and Physical</t>
+          <t>Discharge Medication</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5200,7 +4938,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>History and Physical</t>
+          <t>Discharge Medication</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -5209,18 +4947,13 @@
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Interim Summary</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5230,7 +4963,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Interim Summary</t>
+          <t>Depart/Discharge Note</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -5239,18 +4972,13 @@
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Principal Diagnosis</t>
+          <t>Discharge Summary (class words)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5258,29 +4986,20 @@
           <t>Discharge Summary</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Discharge Diagnosis</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Short Stay Summary</t>
+          <t>Final Case Summary</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5290,7 +5009,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Short Stay Summary</t>
+          <t>Depart/Discharge Note</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5299,18 +5018,13 @@
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Transfer Summary</t>
+          <t>History and Physical</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5320,7 +5034,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Transfer of Care</t>
+          <t>History and Physical</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5329,164 +5043,138 @@
           <t>Discharge</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ADL/IADL flow sheet</t>
+          <t>Interim Summary</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Forms and Questionnaires</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Interim Summary</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Annual Assessments</t>
+          <t>Principal Diagnosis</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Forms and Questionnaires</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Discharge Diagnosis</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Short Stay Summary</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Forms and Questionnaires</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Short Stay Summary</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Transfer Summary</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Forms and Questionnaires</t>
+          <t>Discharge Summary</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Transfer of Care</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>ADL/IADL flow sheet</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Forms and Questionnaires</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Forms and Questionnaires</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Growth Chart</t>
+          <t>Annual Assessments</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5505,18 +5193,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Growth chart</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5532,21 +5215,16 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Medicare annual wellness visit</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5556,27 +5234,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mini-Mental State Exam</t>
+          <t>Forms and Questionnaires</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5584,29 +5257,20 @@
           <t>Forms and Questionnaires</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Questionnaire</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Other Evaluation</t>
+          <t>Growth Chart</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5622,21 +5286,16 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pre Operative Orders</t>
+          <t>Growth chart</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5646,27 +5305,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Medicare annual wellness visit</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5676,27 +5330,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Staying Healthy Assessment</t>
+          <t>Mini-Mental State Exam</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5706,63 +5355,57 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Other Evaluation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Immunization</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Forms and Questionnaires</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Immunization List</t>
+          <t>Pre Operative Orders</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Forms and Questionnaires</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Immunization Record</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5771,28 +5414,23 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Immunization Record</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Forms and Questionnaires</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Immunization Record</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5801,28 +5439,23 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Immunization list</t>
+          <t>Staying Healthy Assessment</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Forms and Questionnaires</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Immunization Record</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5831,18 +5464,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Immunizations</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5850,29 +5478,20 @@
           <t>Immunization</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Immunization Record</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Vaccine Record</t>
+          <t>Immunization List</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5891,154 +5510,113 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Allergies Report</t>
+          <t>Immunization Record</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Allergy Testing Report</t>
-        </is>
-      </c>
+          <t>Immunization Record</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Allergy List</t>
+          <t>Immunization list</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Allergy Testing Report</t>
-        </is>
-      </c>
+          <t>Immunization Record</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Allergy Testing Report</t>
+          <t>Immunizations</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Allergy Testing Report</t>
-        </is>
-      </c>
+          <t>Immunization Record</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Allergy testing report</t>
+          <t>Vaccine Record</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Allergy Testing Report</t>
-        </is>
-      </c>
+          <t>Immunization Record</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ankle-Brachial Index Report</t>
+          <t>Allergies Report</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6048,12 +5626,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ankle-Brachial Index Report</t>
+          <t>Allergy Testing Report</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6061,18 +5639,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Audiogram and Hearing Loss Report</t>
+          <t>Allergy List</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6082,12 +5655,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Audiogram and Hearing Loss Report</t>
+          <t>Allergy Testing Report</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6095,18 +5668,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Behavioral Assessment</t>
+          <t>Allergy Testing Report</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6116,12 +5684,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Behavioral Assessment</t>
+          <t>Allergy Testing Report</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6129,18 +5697,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bone Density (DEXA) Report</t>
+          <t>Allergy testing report</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6150,12 +5713,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bone Mineral Density Report</t>
+          <t>Allergy Testing Report</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6163,18 +5726,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Brain MRI Report</t>
+          <t>Ankle-Brachial Index Report</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6184,12 +5742,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Brain MRI Report</t>
+          <t>Ankle-Brachial Index Report</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6197,18 +5755,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bronchoscopy Report</t>
+          <t>Audiogram and Hearing Loss Report</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6223,7 +5776,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bronchoscopy Report</t>
+          <t>Audiogram and Hearing Loss Report</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6231,18 +5784,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CT Angiography</t>
+          <t>Behavioral Assessment</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6252,12 +5800,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CT Angiography Report</t>
+          <t>Behavioral Assessment</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6265,18 +5813,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CT Scan Report</t>
+          <t>Bone Density (DEXA) Report</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6291,7 +5834,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CT Scan Report</t>
+          <t>Bone Mineral Density Report</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6299,18 +5842,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cardiac Report</t>
+          <t>Brain MRI Report</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6320,12 +5858,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Brain MRI Report</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6333,18 +5871,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Carotid Duplex Report</t>
+          <t>Bronchoscopy Report</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6359,7 +5892,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Carotid Duplex Report</t>
+          <t>Bronchoscopy Report</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6367,18 +5900,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Carotid duplex</t>
+          <t>CT Scan Report</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6388,12 +5916,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Carotid Duplex Report</t>
+          <t>CT Scan Report</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6401,18 +5929,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Cardiac Report</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6422,7 +5945,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6435,18 +5958,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Chemistry Report</t>
+          <t>Carotid Duplex Report</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6456,12 +5974,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Chemistry Report</t>
+          <t>Carotid Duplex Report</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6469,18 +5987,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Corneal Topography</t>
+          <t>Carotid duplex</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6495,7 +6008,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Corneal Topography</t>
+          <t>Carotid Duplex Report</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6503,18 +6016,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cystoscopy Report</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6524,12 +6032,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cystoscopy Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6537,18 +6045,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DPN results</t>
+          <t>Chemistry Report</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6558,12 +6061,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Chemistry Report</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6571,18 +6074,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Doppler Duplex Report</t>
+          <t>Corneal Topography</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6597,7 +6095,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Doppler Duplex Report</t>
+          <t>Corneal Topography</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6605,18 +6103,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EMG report</t>
+          <t>Cystoscopy Report</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6631,7 +6124,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Electromyography and Nerve Conduction</t>
+          <t>Cystoscopy Report</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6639,18 +6132,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Endoscopy report</t>
+          <t>DPN results</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6673,18 +6161,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Esophageal manometry</t>
+          <t>Doppler Duplex Report</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6699,7 +6182,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Esophageal Manometry Report</t>
+          <t>Doppler Duplex Report</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6707,18 +6190,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Esophagogastroduodenoscopy Report</t>
+          <t>EMG report</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6733,7 +6211,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Esophagogastroduodenoscopy (EGD) Report</t>
+          <t>Electromyography and Nerve Conduction</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6741,18 +6219,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FISH Report</t>
+          <t>Endoscopy report</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6762,12 +6235,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FISH Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6775,18 +6248,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gastroenterology / GI</t>
+          <t>Esophageal manometry</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6801,7 +6269,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Esophageal Manometry Report</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6809,18 +6277,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Genetic Test Report</t>
+          <t>Esophagogastroduodenoscopy Report</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6830,12 +6293,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Genetic Test Report</t>
+          <t>Esophagogastroduodenoscopy (EGD) Report</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6843,18 +6306,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Glucose Report</t>
+          <t>FISH Report</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6869,7 +6327,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Glucose Report</t>
+          <t>FISH Report</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6877,18 +6335,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Glucose report</t>
+          <t>Gastroenterology / GI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6898,12 +6351,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Glucose Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6911,18 +6364,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hematology</t>
+          <t>Genetic Test Report</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6937,7 +6385,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Hematology Report</t>
+          <t>Genetic Test Report</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6945,18 +6393,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Hematology Report</t>
+          <t>Glucose Report</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,7 +6414,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Hematology Report</t>
+          <t>Glucose Report</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6979,18 +6422,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Holter Monitor Report</t>
+          <t>Glucose report</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7000,12 +6438,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Holter Monitor Report</t>
+          <t>Glucose Report</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7013,18 +6451,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Holter monitor report</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7034,12 +6467,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Holter Monitor Report</t>
+          <t>Hematology Report</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7047,18 +6480,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INR and Prothrombin Time</t>
+          <t>Hematology Report</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7073,7 +6501,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Coagulation Report</t>
+          <t>Hematology Report</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7081,18 +6509,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Holter Monitor Report</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7100,25 +6523,28 @@
           <t>Lab Report</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Diagnostic Study</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Holter Monitor Report</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Lab Report &gt; Radiology Report</t>
+          <t>Holter monitor report</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7128,57 +6554,55 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Diagnostic Study</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Holter Monitor Report</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>INR and Prothrombin Time</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Lab Report</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>Lab Result</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Lab Report</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Coagulation Report</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Laboratory Flow Sheet</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7186,33 +6610,20 @@
           <t>Lab Report</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Laboratory Flow Sheet</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Laboratory Result</t>
+          <t>Lab Report &gt; Radiology Report</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7222,31 +6633,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lab Result</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
+          <t>Radiology Report</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MR Angiography Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7256,31 +6658,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>MR Angiography Report</t>
-        </is>
-      </c>
+          <t>Lab Result</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MR brain report</t>
+          <t>Laboratory Flow Sheet</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7290,12 +6683,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>Laboratory Flow Sheet</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7303,18 +6696,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>Laboratory Result</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7324,12 +6712,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7337,18 +6725,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>MR Angiography Report</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7358,12 +6741,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Microbiology Report</t>
+          <t>MR Angiography Report</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7371,18 +6754,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Microbiology Report</t>
+          <t>MR brain report</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7392,12 +6770,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Microbiology Report</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7405,18 +6783,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mohs surgery report</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7426,12 +6799,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7439,18 +6812,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Optical Coherence Tomography Report</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7460,12 +6828,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Optical Coherence Tomography Report</t>
+          <t>Microbiology Report</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7473,18 +6841,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Plethysmography Report</t>
+          <t>Microbiology Report</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7494,12 +6857,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Plethysmography Report</t>
+          <t>Microbiology Report</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7507,18 +6870,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Plethysmography report</t>
+          <t>Mohs surgery report</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7528,12 +6886,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Pathology Report</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Plethysmography Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7541,18 +6899,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test</t>
+          <t>Optical Coherence Tomography Report</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7567,7 +6920,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test</t>
+          <t>Optical Coherence Tomography Report</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7575,18 +6928,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pulmonary function test / spirometry</t>
+          <t>Plethysmography Report</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7601,7 +6949,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test</t>
+          <t>Plethysmography Report</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7609,18 +6957,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Plethysmography report</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7630,12 +6973,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mammogram Report</t>
+          <t>Plethysmography Report</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7643,18 +6986,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sigmoidoscopy Report</t>
+          <t>Pulmonary Function Test</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7669,7 +7007,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sigmoidoscopy Report</t>
+          <t>Pulmonary Function Test</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7677,18 +7015,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sonogram Report</t>
+          <t>Pulmonary function test / spirometry</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7698,12 +7031,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Pulmonary Function Test</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7711,18 +7044,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sonogram report</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7737,7 +7065,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Mammogram Report</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7745,18 +7073,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Telemetry Report</t>
+          <t>Sigmoidoscopy Report</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7771,7 +7094,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Telemetry Report</t>
+          <t>Sigmoidoscopy Report</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7779,18 +7102,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tissue Report</t>
+          <t>Sonogram Report</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7800,12 +7118,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7813,18 +7131,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tomography</t>
+          <t>Sonogram report</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7839,7 +7152,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CT Scan Report</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7847,18 +7160,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tomography Report</t>
+          <t>Telemetry Report</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7868,12 +7176,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CT Scan Report</t>
+          <t>Telemetry Report</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7881,18 +7189,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Tissue Report</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7902,12 +7205,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Pathology Report</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7915,18 +7218,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Urinalysis</t>
+          <t>Tomography</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7936,12 +7234,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Urinalysis Report</t>
+          <t>CT Scan Report</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7949,18 +7247,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Urinalysis Report</t>
+          <t>Tomography Report</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7970,12 +7263,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Urinalysis Report</t>
+          <t>CT Scan Report</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7983,18 +7276,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Vascular Studies</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8004,12 +7292,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8017,18 +7305,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>X Ray Report</t>
+          <t>Urinalysis</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8038,12 +7321,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>X-Ray Report</t>
+          <t>Urinalysis Report</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8051,18 +7334,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>X-Ray Report</t>
+          <t>Urinalysis Report</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8072,12 +7350,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>X-Ray Report</t>
+          <t>Urinalysis Report</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8085,104 +7363,100 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Vascular Studies</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Medication Record</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Medication List</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Diagnostic Study</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Medication Reconciliation</t>
+          <t>X Ray Report</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Medication Record</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Medication List</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Radiology Report</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>X-Ray Report</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Medication Record</t>
+          <t>X-Ray Report</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Medication Record</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
+          <t>Lab Report</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Radiology Report</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>X-Ray Report</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Prescription / Rx page</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8201,18 +7475,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Prescription Page</t>
+          <t>Medication Reconciliation</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8222,7 +7491,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prescription Page</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -8231,18 +7500,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Refill Record</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8250,29 +7514,20 @@
           <t>Medication Record</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Refill Record</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Refill record</t>
+          <t>Prescription / Rx page</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8282,7 +7537,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Refill Record</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -8291,28 +7546,23 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ED Triage</t>
+          <t>Prescription Page</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Triage Report</t>
+          <t>Prescription Page</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -8321,118 +7571,98 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Implant Record</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Implant Record</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Intra-operative Record</t>
+          <t>Refill record</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Intra-operative Record</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Post-operative</t>
+          <t>Laboratory Requisition</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Post-operative</t>
+          <t>Laboratory Requisition</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Triage Note</t>
+          <t>Medication Orders</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Triage Report</t>
+          <t>Physician Order</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -8441,18 +7671,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Laboratory Requisition</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8460,29 +7685,20 @@
           <t>Order and Requisition</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Laboratory Requisition</t>
-        </is>
-      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Medication Orders</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8501,44 +7717,38 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>Physician Order</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
           <t>Order and Requisition</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Order and Requisition</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Physician Order</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Post Operative Orders</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8557,18 +7767,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Protocols</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -8578,7 +7783,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -8587,18 +7792,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Post Operative Orders</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8608,7 +7808,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -8617,104 +7817,84 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Protocols</t>
+          <t>Index Page</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Order and Requisition</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
           <t>Others</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Referral Order</t>
+          <t>General Notice</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Order and Requisition</t>
+          <t>Patient Communication</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Referral Order</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Index Page</t>
+          <t>Messages</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>Patient Communication</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Patient Message</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>General Notice</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8733,18 +7913,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Messages</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8763,18 +7938,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Patient Communication</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8782,29 +7952,20 @@
           <t>Patient Communication</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Patient Communication &gt; Telephone Encounter</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8814,7 +7975,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Patient Message</t>
+          <t>Telephone Encounter</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -8823,44 +7984,38 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>Patient Education</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>Patient Communication</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Patient Communication</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Patient Education Material</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Patient Communication &gt; Telephone Encounter</t>
+          <t>Patient Education Material</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8870,7 +8025,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Telephone Encounter</t>
+          <t>Patient Education Material</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -8879,18 +8034,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Patient Education</t>
+          <t>Telephone Message</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8900,7 +8050,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Patient Message</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -8909,28 +8059,23 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Clinical Diagnosis List</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Diagnosis List/Index</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -8939,28 +8084,23 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Telephone Message</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Patient Message</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -8969,18 +8109,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Clinical Diagnosis List</t>
+          <t>Standalone Patient Summary</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8988,39 +8123,30 @@
           <t>Problem List</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Diagnosis List/Index</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Ambulatory Correspondence</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Provider Letter</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -9029,44 +8155,38 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Standalone Patient Summary</t>
+          <t>Consultation Letter</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Problem List</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
+          <t>Provider Letter</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Consultation Letter</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Needs review (document decides)</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>context</t>
-        </is>
-      </c>
+          <t>Non-Codable</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ambulatory Correspondence</t>
+          <t>Letter</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9085,18 +8205,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Consultation Letter</t>
+          <t>Provider Letter (class words)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9104,29 +8219,20 @@
           <t>Provider Letter</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Consultation Letter</t>
-        </is>
-      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Letter</t>
+          <t>Records Request</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9136,7 +8242,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Records Request</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -9145,18 +8251,13 @@
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Provider Letter (class words)</t>
+          <t>Referral Letter</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -9164,85 +8265,24 @@
           <t>Provider Letter</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Referral Letter</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Non-Codable</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Records Request</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Provider Letter</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Records Request</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Non-Codable</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Referral Letter</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Provider Letter</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Referral Letter</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Non-Codable</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>page_type_tag</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Codable,Non-Codable,Discharge,Needs review"</formula1>
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Codable,Non-Codable,Discharge"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9255,7 +8295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9265,7 +8305,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9288,12 +8327,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Demographics</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Face Sheet</t>
+          <t>Pathology Report</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -9301,25 +8340,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Demographics</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Patient Information</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Radiology Report</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CT Angiography Report</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Operative Note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Anesthesia Record</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -9332,7 +8375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anesthesia Record</t>
+          <t>Critical Care Record</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -9345,7 +8388,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Critical Care Record</t>
+          <t>Implant Record</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -9358,7 +8401,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Intra-operative Record</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -9371,7 +8414,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pre-operative</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -9384,7 +8427,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Procedure List</t>
+          <t>Post-operative</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -9397,7 +8440,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Surgery Report</t>
+          <t>Pre-operative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -9410,7 +8453,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Triage Report</t>
+          <t>Procedure List</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -9418,12 +8461,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Procedure Note</t>
+          <t>Operative Note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cardiac Procedure</t>
+          <t>Surgery Report</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -9431,12 +8474,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Procedure Note</t>
+          <t>Operative Note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dialysis Record</t>
+          <t>Triage Report</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -9449,7 +8492,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elastography</t>
+          <t>Cardiac Procedure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -9462,7 +8505,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Endoscopy (EGD)</t>
+          <t>Dialysis Record</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -9475,7 +8518,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Infusion and Chemotherapy</t>
+          <t>Elastography</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -9488,7 +8531,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Injection Visit</t>
+          <t>Endoscopy (EGD)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -9501,7 +8544,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Knee Procedure</t>
+          <t>Infusion and Chemotherapy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -9514,7 +8557,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Laser Procedure</t>
+          <t>Injection Visit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -9527,7 +8570,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lumbar Procedure</t>
+          <t>Knee Procedure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -9540,7 +8583,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Office Procedure</t>
+          <t>Laser Procedure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -9553,7 +8596,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Lumbar Procedure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -9566,7 +8609,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pathology Procedure</t>
+          <t>Office Procedure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -9579,7 +8622,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Radiation Therapy</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -9592,7 +8635,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Therapy Session</t>
+          <t>Pathology Procedure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -9605,7 +8648,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wound Care</t>
+          <t>Radiation Therapy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -9613,12 +8656,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Progress Note</t>
+          <t>Procedure Note</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Assessment and Plan</t>
+          <t>Therapy Session</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -9626,12 +8669,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Progress Note</t>
+          <t>Procedure Note</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CC/HPI</t>
+          <t>Wound Care</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -9644,7 +8687,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lab and Imaging Results</t>
+          <t>Assessment and Plan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -9657,7 +8700,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>CC/HPI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -9670,7 +8713,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Lab and Imaging Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -9683,7 +8726,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Patient Instructions</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -9696,7 +8739,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Physical Exam</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -9709,7 +8752,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Patient Instructions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -9722,7 +8765,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Procedure List</t>
+          <t>Physical Exam</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -9735,7 +8778,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -9748,7 +8791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Procedure List</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -9761,7 +8804,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -9774,7 +8817,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Visit Diagnosis</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -9787,10 +8830,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Progress Note</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Visit Diagnosis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Progress Note</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Vitals</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/codeability_review.xlsx
+++ b/docs/codeability_review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MR Angiography Report</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3148,7 +3148,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MR Angiography Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>MRI Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>Mammogram Report</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3177,7 +3177,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MRI Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Mammogram Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mammogram Report</t>
+          <t>Nuclear Medicine Report</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3206,7 +3206,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Mammogram Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Nuclear Medicine Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>A radiology with no more specific type identified. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3264,7 +3264,7 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>A radiology with no more specific type identified. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Ultrasound Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>X-Ray Report</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3293,26 +3293,22 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ultrasound Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>X-Ray Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>X-Ray Report</t>
-        </is>
-      </c>
+          <t>Blood Transfusion Record</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -3322,7 +3318,7 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>X-Ray Report. Imaging reports: plain film, CT, MRI, ultrasound, mammography, nuclear medicine, bone density. Angiography is held separately from plain CT and MR because it is a different protocol and a different code.</t>
+          <t>Administration of blood or blood products, which is a medication administration rather than a procedure.</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3330,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Blood Transfusion Record</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -3347,7 +3343,7 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Administration of blood or blood products, which is a medication administration rather than a procedure.</t>
+          <t>The current medication list as a standalone page.</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3355,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -3372,7 +3368,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>The current medication list as a standalone page.</t>
+          <t>A medication page that fits none of the above.</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3380,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Prescription Page</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -3397,7 +3393,7 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>A medication page that fits none of the above.</t>
+          <t>A prescription or Rx page.</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Prescription Page</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -3422,19 +3418,19 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>A prescription or Rx page.</t>
+          <t>A record of refills issued.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Medication Record</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Refill Record</t>
+          <t>Laboratory Requisition</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -3447,7 +3443,7 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>A record of refills issued.</t>
+          <t>A requisition or lab form requesting a test.</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3455,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Laboratory Requisition</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -3472,7 +3468,7 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>A requisition or lab form requesting a test.</t>
+          <t>An order or request that fits neither of the above.</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3480,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Physician Order</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -3497,7 +3493,7 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>An order or request that fits neither of the above.</t>
+          <t>Any order written by a clinician: medication, treatment, service request, post-operative orders.</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3505,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -3522,19 +3518,19 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Any order written by a clinician: medication, treatment, service request, post-operative orders.</t>
+          <t>Referral Order.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Order and Requisition</t>
+          <t>Patient Communication</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Referral Order</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -3547,7 +3543,7 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Referral Order.</t>
+          <t>A notice or notification sent to the patient, including discharge notices.</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3555,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -3572,7 +3568,7 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>A notice or notification sent to the patient, including discharge notices.</t>
+          <t>A communication page that fits none of the above.</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3580,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Patient Education Material</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -3597,7 +3593,7 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>A communication page that fits none of the above.</t>
+          <t>Educational material and patient instructions given out as their own document.</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3605,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Patient Message</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -3622,7 +3618,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Educational material and patient instructions given out as their own document.</t>
+          <t>A message exchanged with the patient: telephone message, portal communication, web encounter.</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3630,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Patient Message</t>
+          <t>Telephone Encounter</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3647,19 +3643,19 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>A message exchanged with the patient: telephone message, portal communication, web encounter.</t>
+          <t>Phone note, refill call, telephone message.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Telephone Encounter</t>
+          <t>Diagnosis List/Index</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -3672,7 +3668,7 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phone note, refill call, telephone message.</t>
+          <t>A list or index of diagnoses, often coded, with no assessment.</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3680,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Diagnosis List/Index</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -3697,7 +3693,7 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>A list or index of diagnoses, often coded, with no assessment.</t>
+          <t>Others.</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3705,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -3722,19 +3718,19 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Others.</t>
+          <t>A standing problem list page.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Provider Letter</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Consultation Letter</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -3747,7 +3743,7 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>A standing problem list page.</t>
+          <t>Consultant letter back to the referring provider.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3755,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Consultation Letter</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3772,7 +3768,7 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Consultant letter back to the referring provider.</t>
+          <t>Others.</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3780,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Records Request</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3797,7 +3793,7 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Others.</t>
+          <t>Any letter, fax or EHR note whose purpose is requesting records.</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3805,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Records Request</t>
+          <t>Referral Letter</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3822,38 +3818,13 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Any letter, fax or EHR note whose purpose is requesting records.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Provider Letter</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Referral Letter</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Non-Codable</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
           <t>Letter referring the patient to another provider.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 E106 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E119 E120 E121 E122 E123 E124 E125 E126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 E106 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E119 E120 E121 E122 E123 E124 E125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Codable,Non-Codable,Discharge"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3867,7 +3838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6731,7 +6702,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MR Angiography Report</t>
+          <t>MR brain report</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6746,7 +6717,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MR Angiography Report</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6760,7 +6731,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MR brain report</t>
+          <t>MRI Report</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6789,7 +6760,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6799,12 +6770,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MRI Report</t>
+          <t>Microbiology Report</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6818,7 +6789,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Microbiology Report</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6847,7 +6818,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Microbiology Report</t>
+          <t>Mohs surgery report</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6857,12 +6828,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Pathology Report</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Microbiology Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6876,7 +6847,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Mohs surgery report</t>
+          <t>Optical Coherence Tomography Report</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6886,12 +6857,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Optical Coherence Tomography Report</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6905,7 +6876,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Optical Coherence Tomography Report</t>
+          <t>Plethysmography Report</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6920,7 +6891,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Optical Coherence Tomography Report</t>
+          <t>Plethysmography Report</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6934,7 +6905,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Plethysmography Report</t>
+          <t>Plethysmography report</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6963,7 +6934,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Plethysmography report</t>
+          <t>Pulmonary Function Test</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6978,7 +6949,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Plethysmography Report</t>
+          <t>Pulmonary Function Test</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6992,7 +6963,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test</t>
+          <t>Pulmonary function test / spirometry</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7021,7 +6992,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pulmonary function test / spirometry</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7031,12 +7002,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pulmonary Function Test</t>
+          <t>Mammogram Report</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7050,7 +7021,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Sigmoidoscopy Report</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7060,12 +7031,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mammogram Report</t>
+          <t>Sigmoidoscopy Report</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7079,7 +7050,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sigmoidoscopy Report</t>
+          <t>Sonogram Report</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7089,12 +7060,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sigmoidoscopy Report</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7108,7 +7079,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sonogram Report</t>
+          <t>Sonogram report</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7137,7 +7108,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sonogram report</t>
+          <t>Telemetry Report</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7147,12 +7118,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Telemetry Report</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7166,7 +7137,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Telemetry Report</t>
+          <t>Tissue Report</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7176,12 +7147,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Pathology Report</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Telemetry Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7195,7 +7166,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tissue Report</t>
+          <t>Tomography</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7205,12 +7176,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pathology Report</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>CT Scan Report</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7224,7 +7195,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tomography</t>
+          <t>Tomography Report</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7253,7 +7224,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tomography Report</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7268,7 +7239,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>CT Scan Report</t>
+          <t>Ultrasound Report</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7282,7 +7253,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Urinalysis</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7292,12 +7263,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
+          <t>Lab Result</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ultrasound Report</t>
+          <t>Urinalysis Report</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7311,7 +7282,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Urinalysis</t>
+          <t>Urinalysis Report</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7340,7 +7311,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Urinalysis Report</t>
+          <t>Vascular Studies</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7350,12 +7321,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lab Result</t>
+          <t>Diagnostic Study</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Urinalysis Report</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7369,7 +7340,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Vascular Studies</t>
+          <t>X Ray Report</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7379,12 +7350,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Diagnostic Study</t>
+          <t>Radiology Report</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>X-Ray Report</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7398,7 +7369,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>X Ray Report</t>
+          <t>X-Ray Report</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7427,24 +7398,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>X-Ray Report</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lab Report</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Radiology Report</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>X-Ray Report</t>
-        </is>
-      </c>
+          <t>Medication List</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Non-Codable</t>
@@ -7456,7 +7423,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Medication Reconciliation</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7481,7 +7448,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Medication Reconciliation</t>
+          <t>Medication Record</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7489,11 +7456,7 @@
           <t>Medication Record</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Medication List</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
@@ -7506,15 +7469,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>Prescription / Rx page</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>Medication Record</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Medication Record</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Medication List</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
@@ -7527,7 +7494,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Prescription / Rx page</t>
+          <t>Prescription Page</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7537,7 +7504,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Prescription Page</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -7552,7 +7519,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Prescription Page</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7562,7 +7529,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prescription Page</t>
+          <t>Refill Record</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -7577,7 +7544,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Refill Record</t>
+          <t>Refill record</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7602,17 +7569,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Refill record</t>
+          <t>Laboratory Requisition</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Medication Record</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Refill Record</t>
+          <t>Laboratory Requisition</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -7627,7 +7594,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Laboratory Requisition</t>
+          <t>Medication Orders</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7637,7 +7604,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Laboratory Requisition</t>
+          <t>Physician Order</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -7652,7 +7619,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Medication Orders</t>
+          <t>Order and Requisition</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7660,11 +7627,7 @@
           <t>Order and Requisition</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Physician Order</t>
-        </is>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
@@ -7677,15 +7640,19 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>Order and Requisition</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Order and Requisition</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Physician Order</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
@@ -7698,7 +7665,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Physician Order</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7723,7 +7690,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Post Operative Orders</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7748,7 +7715,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Post Operative Orders</t>
+          <t>Protocols</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7758,7 +7725,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Physician Order</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -7773,7 +7740,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Protocols</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7783,7 +7750,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -7798,19 +7765,15 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Referral Order</t>
+          <t>Index Page</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Order and Requisition</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Referral Order</t>
-        </is>
-      </c>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
@@ -7823,15 +7786,19 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Index Page</t>
+          <t>General Notice</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>Patient Communication</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
@@ -7844,7 +7811,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>General Notice</t>
+          <t>Messages</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7854,7 +7821,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Patient Message</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -7869,7 +7836,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Messages</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7879,7 +7846,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Patient Message</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -7894,7 +7861,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7904,7 +7871,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Patient Message</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -7919,7 +7886,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Patient Communication</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7927,11 +7894,7 @@
           <t>Patient Communication</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Patient Message</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
@@ -7944,15 +7907,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>Patient Communication &gt; Telephone Encounter</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
           <t>Patient Communication</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Patient Communication</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Telephone Encounter</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
@@ -7965,7 +7932,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Patient Communication &gt; Telephone Encounter</t>
+          <t>Patient Education</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7975,7 +7942,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Telephone Encounter</t>
+          <t>Patient Education Material</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -7990,7 +7957,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Patient Education</t>
+          <t>Patient Education Material</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8015,7 +7982,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Telephone Message</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8025,7 +7992,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Patient Education Material</t>
+          <t>Patient Message</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -8040,17 +8007,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Telephone Message</t>
+          <t>Clinical Diagnosis List</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Patient Message</t>
+          <t>Diagnosis List/Index</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -8065,7 +8032,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Clinical Diagnosis List</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8075,7 +8042,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Diagnosis List/Index</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -8090,19 +8057,15 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>Standalone Patient Summary</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>Problem List</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Problem List</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Problem List</t>
-        </is>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
@@ -8115,15 +8078,19 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Standalone Patient Summary</t>
+          <t>Ambulatory Correspondence</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Problem List</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>Provider Letter</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
@@ -8136,7 +8103,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ambulatory Correspondence</t>
+          <t>Consultation Letter</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8146,7 +8113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Consultation Letter</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -8161,7 +8128,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Consultation Letter</t>
+          <t>Letter</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8171,7 +8138,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Consultation Letter</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -8186,7 +8153,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Letter</t>
+          <t>Provider Letter (class words)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8194,11 +8161,7 @@
           <t>Provider Letter</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
@@ -8211,7 +8174,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Provider Letter (class words)</t>
+          <t>Records Request</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8219,7 +8182,11 @@
           <t>Provider Letter</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Records Request</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
@@ -8232,7 +8199,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Records Request</t>
+          <t>Referral Letter</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8242,7 +8209,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Records Request</t>
+          <t>Referral Letter</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -8254,34 +8221,9 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Referral Letter</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Provider Letter</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Referral Letter</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Non-Codable</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Codable,Non-Codable,Discharge"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8295,7 +8237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8357,15 +8299,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Lab Report</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anesthesia Record</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Radiology Report</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MR Angiography Report</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8375,7 +8321,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Critical Care Record</t>
+          <t>Anesthesia Record</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -8388,7 +8334,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Implant Record</t>
+          <t>Critical Care Record</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -8401,7 +8347,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intra-operative Record</t>
+          <t>Implant Record</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -8414,7 +8360,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Intra-operative Record</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -8427,7 +8373,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Post-operative</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -8440,7 +8386,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pre-operative</t>
+          <t>Post-operative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -8453,7 +8399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Procedure List</t>
+          <t>Pre-operative</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -8466,7 +8412,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Surgery Report</t>
+          <t>Procedure List</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -8479,7 +8425,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Triage Report</t>
+          <t>Surgery Report</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -8487,12 +8433,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Procedure Note</t>
+          <t>Operative Note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cardiac Procedure</t>
+          <t>Triage Report</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -8505,7 +8451,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dialysis Record</t>
+          <t>Cardiac Procedure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -8518,7 +8464,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elastography</t>
+          <t>Dialysis Record</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -8531,7 +8477,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Endoscopy (EGD)</t>
+          <t>Elastography</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -8544,7 +8490,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Infusion and Chemotherapy</t>
+          <t>Endoscopy (EGD)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -8557,7 +8503,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Injection Visit</t>
+          <t>Infusion and Chemotherapy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -8570,7 +8516,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Knee Procedure</t>
+          <t>Injection Visit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -8583,7 +8529,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Laser Procedure</t>
+          <t>Knee Procedure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -8596,7 +8542,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lumbar Procedure</t>
+          <t>Laser Procedure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -8609,7 +8555,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Office Procedure</t>
+          <t>Lumbar Procedure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -8622,7 +8568,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Office Procedure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -8635,7 +8581,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pathology Procedure</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -8648,7 +8594,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Radiation Therapy</t>
+          <t>Pathology Procedure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -8661,7 +8607,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Therapy Session</t>
+          <t>Radiation Therapy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -8674,7 +8620,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wound Care</t>
+          <t>Therapy Session</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -8682,12 +8628,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Progress Note</t>
+          <t>Procedure Note</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Assessment and Plan</t>
+          <t>Wound Care</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -8700,7 +8646,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CC/HPI</t>
+          <t>Assessment and Plan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -8713,7 +8659,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lab and Imaging Results</t>
+          <t>CC/HPI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -8726,7 +8672,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Lab and Imaging Results</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -8739,7 +8685,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -8752,7 +8698,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Patient Instructions</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -8765,7 +8711,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Physical Exam</t>
+          <t>Patient Instructions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -8778,7 +8724,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Problem List</t>
+          <t>Physical Exam</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -8791,7 +8737,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procedure List</t>
+          <t>Problem List</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -8804,7 +8750,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Questionnaire</t>
+          <t>Procedure List</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -8817,7 +8763,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Questionnaire</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -8830,7 +8776,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -8843,7 +8789,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visit Diagnosis</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -8856,10 +8802,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Visit Diagnosis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Progress Note</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Vitals</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
